--- a/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800724C3-BFFC-4972-9702-E030C798510F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8E2FD7-9A33-43E7-B8EF-B834872E4A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>Name</t>
   </si>
@@ -148,6 +148,72 @@
   </si>
   <si>
     <t>对自己添加正面效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击X2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击X3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>对玩家造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0}X2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>对玩家造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{0}X3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackX2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackX3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -701,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -828,11 +894,46 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" tooltip="策略(状态)" display="https://sts2.huijiwiki.com/wiki/%E7%AD%96%E7%95%A5(%E7%8A%B6%E6%80%81)" xr:uid="{2EE2F399-C7DA-419F-A3DF-BB5694AB8488}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/IntentConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8E2FD7-9A33-43E7-B8EF-B834872E4A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4042E148-CB5A-43EB-AFAC-3E5ADF1095A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IntentConfig" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>Name</t>
   </si>
@@ -55,15 +55,6 @@
   </si>
   <si>
     <t>描述</t>
-  </si>
-  <si>
-    <t>attack</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>Attack</t>
   </si>
   <si>
     <t>Id</t>
@@ -214,6 +205,34 @@
   </si>
   <si>
     <t>AttackX3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sleep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉睡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sleep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人这回合什么都不做。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -767,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -777,10 +796,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -811,10 +830,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -827,106 +846,130 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>30</v>
-      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
